--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -868,78 +868,78 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TRIATHLON TRANSFER GMBH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C6" s="2" t="n">
         <v>130.34</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Nein - Finanzamt (steuerneutral)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Triathlon Miete.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Receipt-2265-8647.pdf</t>
+          <t>Invoice-GMM5S7YE-0001.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1891,17 +1891,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Invoice-GMM5S7YE-0001.pdf</t>
+          <t>Receipt-2265-8647.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
+          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
+          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
+          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,17 +2287,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
+          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2649,83 +2649,83 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Haufe Service Center GmbH via Mollie</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Benito Ferrise</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Benito Ferrise</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH via Mollie</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
         </is>
       </c>
     </row>
@@ -2961,10 +2961,10 @@
         <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>180.07</v>
+        <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-80.06999999999999</v>
+        <v>-498.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2980,13 +2980,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>389.06</v>
+        <v>502.3</v>
       </c>
       <c r="D10" t="n">
-        <v>-389.06</v>
+        <v>-502.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2474.29</v>
+        <v>3005.68</v>
       </c>
     </row>
     <row r="17">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2475.71</v>
+        <v>1944.32</v>
       </c>
     </row>
     <row r="18">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19"/>
@@ -4827,7 +4827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4923,134 +4923,138 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Domain webwokr.pdf</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Wix.com LTD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | Domain webwokr.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Google Workspace 2025.pdf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wix.com LTD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | Google Workspace 2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>3.63</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>FINDYLEAD.COM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>39</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Apify_Invoice_202508060773.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>APIFY* SUBSCRIPTION</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.84</v>
+        <v>78.38</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+          <t>Nein - Finanzamt (steuerneutral)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5061,19 +5065,19 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5082,7 +5086,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.9</v>
+        <v>39</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5096,64 +5100,60 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lexoffice 08 25.pdf</t>
+          <t>Apify_Invoice_202508060773.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haufe Service Center GmbH</t>
+          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
+          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Invoice-BCE54405-0015.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>UZR*digistore24.com</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5161,6 +5161,9 @@
           <t>Ausgabe</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>21.9</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -5173,174 +5176,254 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Premium Paket 2025.pdf</t>
+          <t>Lexoffice 08 25.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Wix.com</t>
+          <t>Haufe Service Center GmbH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Wix.com</t>
+          <t>6188.9190.1138 Haufe Service Center | GmbH lx2025080091462 KHYY-YNLG | Lexware Office L | 6894021e166c0474c60b1a89 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0015.pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>240</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Premium Paket 2025.pdf</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wix.com</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Wix.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>100</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Rechnung Joel Wagner.pdf</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Joel Wagner</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>47</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Funnelcockpit_2.pdf</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Umsatz netto:</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Ausgabe netto:</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>180.07</v>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-80.06999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Ausgabe netto:</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>598.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>GEWINN/VERLUST:</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-498.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C19" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5355,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -5364,7 +5447,7 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="53" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -5571,36 +5654,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rechnung_RE0009 (1).pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Hotel Melia Frankfurt am Main | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
@@ -5689,158 +5776,198 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LNKD_INVOICE_789144507558.pdf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LinkedIn Ireland Unlimited Company</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PRIVAT BEZAHLT (kein Geschaeftskonto) - Einlage | LNKD_INVOICE_789144507558.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>0.84</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>IONOS Rechnung 2025-09-13 - RG_100171679573 (1).pdf</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>IONOS SE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>7.55</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>47</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Rechnung_TJC9SRX6_I-74230203-de.pdf</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Umsatz netto:</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>Umsatz netto:</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>389.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-389.06</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>GEWINN/VERLUST:</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-502.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2</v>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -2904,10 +2904,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>172.9</v>
+        <v>167.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-172.9</v>
+        <v>-167.9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2942,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>156.69</v>
+        <v>151.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-156.69</v>
+        <v>-151.69</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3005.68</v>
+        <v>2995.68</v>
       </c>
     </row>
     <row r="17">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1944.32</v>
+        <v>1954.32</v>
       </c>
     </row>
     <row r="18">
@@ -3790,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3798,7 +3798,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4088,7 +4088,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>17.73</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4106,103 +4106,63 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
+          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fee for extra services provided during 29 Apr | - 28 May, 2025. Inv. No. 3OJ3-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>172.9</v>
+        <v>-167.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-172.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4484,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4492,7 +4452,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4735,84 +4695,44 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PNL Fintech B.V.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Fee for extra services provided during 29 Jun | - 28 Jul, 2025. Inv. No. 3OJ3-0004</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>156.69</v>
+        <v>-151.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-156.69</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,14 +49,11 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +72,6 @@
         <bgColor rgb="001F2937"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,15 +85,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1191,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1407,45 +1397,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>OPENAI</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>H_32869079.pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1454,7 +1448,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.16</v>
+        <v>25</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,33 +1462,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>H_32869079.pdf</t>
+          <t>Triathlon Miete.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,100 +1502,100 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Triathlon Miete.pdf</t>
+          <t>Rechnung RE250007.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>425</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250007.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Google Workspace</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>H_33541164.pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>hostinger.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1610,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.99</v>
+        <v>97.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,99 +1618,59 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>H_33541164.pdf</t>
+          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
+          <t>PNL Fintech B.V.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hostinger.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PNL Fintech B.V.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
           <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>425</v>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>425</v>
+        <v>720.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>728.88</v>
+        <v>-295.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-303.88</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2304,7 +2258,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2313,7 +2267,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.92</v>
+        <v>11</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,24 +2281,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(kein Originalbeleg - akzeptiert)</t>
+          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2353,7 +2307,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,24 +2321,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
+          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2393,7 +2347,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2407,100 +2361,100 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
+          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE*WORKSPACE</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Bagatelle &lt; 10 EUR ohne Beleg</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>GOOGLE*WORKSPACE</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>GOOGLE*WORKSPACE</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Triathlon Miete.pdf</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TRIATHLON TRANSFER GMBH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2509,7 +2463,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>17.99</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,33 +2477,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Triathlon Miete.pdf</t>
+          <t>H_34974301.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
+          <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17.99</v>
+        <v>4000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2563,210 +2517,170 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>H_34974301.pdf</t>
+          <t>Rechnung RE250009.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>Joel Wagner</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rechnung RE250009.pdf</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Joel Wagner</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>NEIN - fehlt</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Benito Ferrise</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Umsatz</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Haufe Service Center GmbH via Mollie</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>NEIN - fehlt</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>97ea7bc1-9f7c-470d-a996-5cf104d13ad4.pdf</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH via Mollie</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>lx2025120363416 KHYY-YNLG Lexware | Office XL 694ff4da0c16582b0d804875 | IBAN: DE39120700700037268718 | BIC: DEUTDEFFXXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Durchlaufposten (Rundlauf-Buchung)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Benito Ferrise</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Durchlaufender Posten | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+    </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4000</v>
+        <v>189.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>207.23</v>
+        <v>3810.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3792.77</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2885,13 +2799,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>98.15000000000001</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-98.15000000000001</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3018,13 +2932,13 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>728.88</v>
+        <v>720.24</v>
       </c>
       <c r="D12" t="n">
-        <v>-303.88</v>
+        <v>-295.24</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3037,10 +2951,10 @@
         <v>4000</v>
       </c>
       <c r="C13" t="n">
-        <v>207.23</v>
+        <v>189.31</v>
       </c>
       <c r="D13" t="n">
-        <v>3792.77</v>
+        <v>3810.69</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -3048,55 +2962,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GESAMTUMSATZ netto (Jahr):</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>4950</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>GESAMTAUSGABEN netto (Jahr):</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>2995.68</v>
+      <c r="B16" s="4" t="n">
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>GESAMTNETTOGEWINN/-VERLUST (Jahr):</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>1954.32</v>
+      <c r="B17" s="4" t="n">
+        <v>1991.68</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>davon Zahlungen ohne Beleg (Jahr):</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>16</v>
+      <c r="B18" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>HINWEIS: Melia-Hotel-Rechnung (Benito Ferrise, 82,99 EUR, 11.09.) ist noch offen -</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>sobald gefunden, muss diese Gesamtrechnung neu berechnet werden.</t>
         </is>
@@ -3527,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3583,45 +3497,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>ZOHO-ZOHO CORP</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>ZOHO-ZOHO CORP</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ausgabe</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Instantly 04 25.pdf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3630,7 +3548,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.13</v>
+        <v>33.32</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3644,7 +3562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Instantly 04 25.pdf</t>
+          <t>Instantly 041 25.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3661,7 +3579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3670,7 +3588,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33.32</v>
+        <v>19.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3679,104 +3597,64 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Instantly 041 25.pdf</t>
+          <t>Lexoffice 04 25.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Haufe Service Center GmbH</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ausgabe</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lexoffice 04 25.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Haufe Service Center GmbH</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>6081.7571.6196 Haufe Service Center | GmbH lx2025040088805 KHYY-YNLG | Lexware Office L | 67f32b8cb70fd8129780e042 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Umsatz netto:</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Umsatz netto:</t>
+          <t>Ausgabe netto:</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Ausgabe netto:</t>
+          <t>GEWINN/VERLUST:</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>98.15000000000001</v>
+        <v>-87.34999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GEWINN/VERLUST:</t>
+          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-98.15000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>davon Zahlungen ohne Beleg (rot, Netto geschaetzt mit 19% USt):</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -93,7 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2695,10 +2694,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -2999,21 +2998,6 @@
       </c>
       <c r="B18" s="4" t="n">
         <v>14</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>HINWEIS: Melia-Hotel-Rechnung (Benito Ferrise, 82,99 EUR, 11.09.) ist noch offen -</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>sobald gefunden, muss diese Gesamtrechnung neu berechnet werden.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>598.22</v>
+        <v>698.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-498.22</v>
+        <v>-698.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="16">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2958.32</v>
+        <v>3058.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1991.68</v>
+        <v>1791.68</v>
       </c>
     </row>
     <row r="18">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Umsatz</t>
+          <t>Ausgabe</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>598.22</v>
+        <v>698.22</v>
       </c>
     </row>
     <row r="18">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-498.22</v>
+        <v>-698.22</v>
       </c>
     </row>
     <row r="19">

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>698.22</v>
+        <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-698.22</v>
+        <v>-498.22</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="16">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3058.32</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1791.68</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="18">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ausgabe</t>
+          <t>Umsatz</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>698.22</v>
+        <v>598.22</v>
       </c>
     </row>
     <row r="18">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-698.22</v>
+        <v>-498.22</v>
       </c>
     </row>
     <row r="19">

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>97.2</v>
+        <v>115.67</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>720.24</v>
+        <v>738.71</v>
       </c>
     </row>
     <row r="15">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-295.24</v>
+        <v>-313.71</v>
       </c>
     </row>
     <row r="16">
@@ -2931,10 +2931,10 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>720.24</v>
+        <v>738.71</v>
       </c>
       <c r="D12" t="n">
-        <v>-295.24</v>
+        <v>-313.71</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2958.32</v>
+        <v>2976.79</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1991.68</v>
+        <v>1973.21</v>
       </c>
     </row>
     <row r="18">

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -688,7 +688,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -897,36 +897,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>130.34</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
     </row>
     <row r="14">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
     </row>
     <row r="16">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2852,16 +2852,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="C8" t="n">
         <v>151.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2871,16 +2871,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
       <c r="C9" t="n">
         <v>598.22</v>
       </c>
       <c r="D9" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2909,16 +2909,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
       <c r="C11" t="n">
         <v>237.17</v>
       </c>
       <c r="D11" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
     </row>
     <row r="16">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="18">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4312,8 +4312,8 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -4522,36 +4522,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="9">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
     </row>
     <row r="11">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4616,7 +4616,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -4821,36 +4821,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>78.38</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Nein - Finanzamt (steuerneutral)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NEIN - fehlt</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="C6" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A (Finanzamt-Erstattung, kein Beleg noetig)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
     </row>
     <row r="17">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
     </row>
     <row r="19">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
+++ b/Finanzen/2025/ergebnis_2025_monatlich_netto.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115.67</v>
+        <v>97.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
     </row>
     <row r="15">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
     </row>
     <row r="16">
@@ -2931,10 +2931,10 @@
         <v>425</v>
       </c>
       <c r="C12" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
       <c r="D12" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="17">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="18">
